--- a/Data/哈基夜的绮罗服装扩展 - 3750208980/1.6/哈基夜的绮罗服装扩展 - 3750208980.xlsx
+++ b/Data/哈基夜的绮罗服装扩展 - 3750208980/1.6/哈基夜的绮罗服装扩展 - 3750208980.xlsx
@@ -64,6 +64,54 @@
     <x:t>신발</x:t>
   </x:si>
   <x:si>
+    <x:t>ApparelLayerDef+Item.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소지품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ApparelLayerDef+Kiiro_TailAccessoryLayer.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_TailAccessoryLayer.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꼬리 장식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RecipeDef+CYQAQ_InstallOriginiumBrainStem_Kiiro.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RecipeDef</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYQAQ_InstallOriginiumBrainStem_Kiiro.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오리지늄 뇌간 이식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RecipeDef+CYQAQ_InstallOriginiumBrainStem_Kiiro.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYQAQ_InstallOriginiumBrainStem_Kiiro.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인공 오리지늄 기관을 뇌에 이식합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RecipeDef+CYQAQ_InstallOriginiumBrainStem_Kiiro.jobString</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYQAQ_InstallOriginiumBrainStem_Kiiro.jobString</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오리지늄 뇌간 이식 중.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ThingDef+Occatcape.label</x:t>
   </x:si>
   <x:si>
@@ -85,6 +133,24 @@
     <x:t>깔끔하게 드리운 형태, 부드러운 포인트 장식, 작은 고양이 장식이 더해진 어두운 정장풍 매니저 망토입니다. 매니저 제복 위에 걸쳐 대화, 거래, 감독 중 착용자에게 침착하고 높은 지위의 인상을 줍니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenBackpack.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenBackpack.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 초등학교 가방</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenBackpack.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenBackpack.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이를 위해 만든 튼튼한 통학 가방입니다. 어깨끈이 단단히 고정되고, 교과서와 공책, 필기구를 정리해 넣을 만한 공간이 넉넉합니다. 옆쪽에는 방범 경보기가 달려 있어 위험한 상황에서 곧바로 주변에 알릴 수 있습니다. 운반 능력을 늘려 주고, 착용자가 안심하고 공부할 마음을 갖게 해 줍니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ThingDef+Kiiro_AliceShoe.label</x:t>
   </x:si>
   <x:si>
@@ -157,6 +223,186 @@
     <x:t>키이로 기모노 게타 아래에 신도록 설계된 전통 타비 양말입니다. 단순한 갈라진 발가락 형태로 기모노 세트를 완성합니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>ThingDef+Kiiro_MaryJane.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_MaryJane.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 메리 제인 구두</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_MaryJane.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_MaryJane.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 원피스에 맞춰 만든 단순한 메리 제인 구두입니다. 단정한 스트랩 설계가 차분한 일상 차림을 완성하면서도 발걸음을 가볍게 유지해 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_CuffSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_CuffSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 접단 양말</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_CuffSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_CuffSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 원피스와 메리 제인 구두에 맞추도록 설계된, 발목을 접어 신는 종아리 길이 양말입니다. 차림 전체에 깔끔하고 부드러운 디테일을 더해 한 벌을 시각적으로 완성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_HighHeels.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_HighHeels.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 하이힐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_HighHeels.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_HighHeels.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧은 치파오에 맞춰 만든 하이힐입니다. 가늘고 격식 있는 형태가 차림을 완성하며, 착용자를 우아하게 차려입은 모습으로 보이게 합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_GarterStockings.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_GarterStockings.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 가터 스타킹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_GarterStockings.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_GarterStockings.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단정하고 우아한 실루엣을 갖춘 고급 가터 스타킹입니다. 격식 있는 차림의 섬세한 속층으로 설계되어, 평상복 아래에 다듬어진 우아한 디테일을 더합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_MidSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_MidSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 중목 양말</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_MidSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_MidSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔한 교복풍 스타일의 단순한 중목 양말입니다. 다리에 단정한 층을 더하며 교복과 로퍼에 자연스럽게 어울립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Loafers.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Loafers.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 로퍼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Loafers.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Loafers.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교복 차림에 맞춰 만든 단정한 로퍼입니다. 단순하고 격식 있는 형태가 교복 한 벌을 완성하면서도 움직임을 편안하게 유지해 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenSocks.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 초등학교 양말</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenSocks.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초등학교 교복에 맞춘 아이용 양말입니다. 깔끔한 길이와 부드러운 형태가 다리 쪽 차림을 완성해, 단정하고 학구적인 분위기를 지켜 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 초등학교 신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등굣길 아이를 위한 작고 단정한 신발입니다. 안정적이고 가벼운 형태 덕분에 교실과 복도, 운동장을 오가기 편하며, 착용자를 편안하고 차분하게 해 전반적인 학습 능력을 조금 끌어올립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 물고기 신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물고기 테마 한 벌에 맞춰 설계한 가벼운 신발입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkShoes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 상어 신발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkShoes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상어 가죽 수영복에 맞춰 만든 아담한 상어 테마 신발입니다. 키이로 상어 한 벌을 머리부터 꼬리까지 균형 있게 잡아 줍니다. 설계자는 이것을 「심해 하키 상어에서 온 보습 슈트」라고 부르지만, 키이로에게 보습이 왜 필요할까요?</x:t>
+  </x:si>
+  <x:si>
     <x:t>ThingDef+ShopUniform.label</x:t>
   </x:si>
   <x:si>
@@ -175,22 +421,22 @@
     <x:t>줄무늬 셔츠, 실용적인 앞치마, 부드러운 치마 실루엣을 갖춘 단정한 제빵점 제복입니다. 제빵, 계산대 업무, 정돈된 일상 작업에 어울리는 따뜻하고 친근한 점원 이미지를 줍니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>ThingDef+Kidscape.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kidscape.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 어린이 망토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kidscape.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kidscape.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>겹겹의 천과 장난스러운 고양이 장식으로 만든 어린이용 작은 망토 의상입니다. 귀엽고 활기찬 실루엣을 유지하면서 어린 정착민에게 가볍고 따뜻한 일상복을 제공합니다.</x:t>
+    <x:t>ThingDef+LolitaDress.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LolitaDress.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 로리타 드레스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+LolitaDress.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LolitaDress.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>겹겹의 치마와 섬세한 장식, 장난스러운 고양이 디테일을 갖춘 아이용 로리타풍 드레스입니다. 가볍고 편안한 재단 덕분에 어린 정착민이 일상복과 나들이옷 어느 쪽으로 입어도 사랑스럽고 활기차 보입니다.</x:t>
   </x:si>
   <x:si>
     <x:t>ThingDef+Lawcat.label</x:t>
@@ -319,6 +565,492 @@
     <x:t>겹쳐 입는 예복, 묶은 오비, 우아한 전통 실루엣을 갖춘 격식 있는 기모노입니다. 착용자를 약간 느리게 하지만, 우아한 형태 덕분에 의식, 사교 방문, 세련된 일상복에 잘 어울립니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>ThingDef+Kiiro_NurseUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NurseUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 간호사 제복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NurseUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NurseUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단정한 의료 실루엣과 실용적인 재단을 갖춘 깨끗한 흰색과 파랑색 간호사 제복입니다. 병동과 진료소에서 믿음직해 보이며, 치료와 응급처치 중 빠르게 움직일 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Dress.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Dress.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 원피스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Dress.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Dress.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 블라우스와 치마 실루엣, 섬세한 일상 스타일을 갖춘 깔끔한 흰색 원피스입니다. 착용자에게 일상에 어울리는 차분하고 우아한 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NunHabit.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NunHabit.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 수녀복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NunHabit.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NunHabit.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴 치마와 정숙한 종교적 실루엣을 갖춘 엄숙한 흑백 수녀복입니다. 일상과 간병, 기도에 어울리는 조용하고 경건한 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_ShortQipao.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_ShortQipao.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 짧은 치파오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_ShortQipao.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_ShortQipao.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔하게 몸에 맞는 실루엣과 우아한 동양풍 스타일을 갖춘 짧은 치파오입니다. 격식 있는 우아함을 주면서도 일상적으로 움직이기에 충분히 가볍습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_OfficeLadyUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_OfficeLadyUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 사무직 제복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_OfficeLadyUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_OfficeLadyUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>격식 있는 직장 실루엣과 단정한 전문직 스타일을 갖춘 사무직 제복입니다. 접객과 협상, 일상 업무에 어울리는 침착하고 유능한 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SchoolUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SchoolUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 교복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SchoolUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SchoolUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀여운 고양이 디자인을 넣은 단정한 교복입니다. 정돈된 옷깃과 주름 디테일, 활기찬 학생 실루엣이 특징입니다. 일상생활과 사교에 어울리는 밝고 앳된 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SchoolSkirt.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SchoolSkirt.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 교복 치마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SchoolSkirt.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SchoolSkirt.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교복 상의에 맞추도록 설계한 주름치마입니다. 단정한 주름과 활기찬 실루엣이 학생 차림을 완성하면서도 움직임을 편안하게 유지해 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_WaitressUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_WaitressUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 종업원 제복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_WaitressUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_WaitressUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔한 접객 중심 실루엣과 친근한 전문직 스타일을 갖춘 단정한 종업원 제복입니다. 손님 응대와 서비스에 어울리는 상냥하고 유능한 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_HighSchoolUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_HighSchoolUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 고등학교 교복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_HighSchoolUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_HighSchoolUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔한 학생 실루엣과 단순한 일상 스타일을 갖춘 단정한 고등학교 교복입니다. 매일 입도록 만들어졌으며 중목 양말, 로퍼와 자연스럽게 어울립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 초등학교 교복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가볍고 단정한 학생 실루엣을 갖춘 아이용 초등학교 통학 교복입니다. 일상적인 움직임과 교실 생활에 편안하며, 어린 착용자를 단정해 보이게 하고 전반적인 학습 능력을 조금 끌어올립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishClothes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishClothes.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 물고기 옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishClothes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishClothes.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물고기 테마 한 벌에 맞춰 설계한 가벼운 수생 의상입니다. 원래의 물고기 고양이 의상 그림을 그대로 살리면서 이 모드의 의복 구조를 따릅니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkSwimsuit.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkSwimsuit.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 상어 수영복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkSwimsuit.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkSwimsuit.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>날렵한 상어 가죽 수영복으로, 활동적인 바다 사냥꾼 같은 인상을 줍니다. 키이로 상어 한 벌의 중심이 되며 상어 신발, 상어 꼬리와 함께 입어 수생 차림을 완성하도록 만들어졌습니다. 설계자는 이것을 「심해 하키 상어에서 온 보습 슈트」라고 부르지만, 키이로에게 보습이 왜 필요할까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+RhodesIslandUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RhodesIslandUniform.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 로도스 아일랜드 제식 제복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+RhodesIslandUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RhodesIslandUniform.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로도스 아일랜드가 키이로를 위해 만든 제식 겉옷 제복입니다. 깔끔하고 실용적인 설계가 일상 근무와 현장 작전 사이의 균형을 잡아, 유능하고 믿음직한 전문가다운 인상을 줍니다. 물망초 - XXX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+RhodesIslandUniformLining.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RhodesIslandUniformLining.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 로도스 아일랜드 제식 제복 내피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+RhodesIslandUniformLining.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RhodesIslandUniformLining.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로도스 아일랜드가 키이로를 위해 만든 가볍고 신축성 있는 제식 제복 내피입니다. 일상 근무 때는 단독으로, 현장 작전 때는 제식 제복 안에 받쳐 입을 수 있습니다. 물망초 - XXX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Cookercap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cookercap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 셰프 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Cookercap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cookercap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드럽고 둥근 형태와 깔끔한 주방 스타일을 갖춘 가벼운 셰프 모자입니다. 셰프 제복을 완성하며 착용자를 깨끗하고 단정하며 주방 일을 할 준비가 된 모습으로 보이게 합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+LolitaDressBow.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LolitaDressBow.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 로리타 드레스 리본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+LolitaDressBow.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LolitaDressBow.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로리타 드레스와 어울리도록 만든 작고 어두운 리본 장식 한 쌍입니다. 머리 양옆에 단정하고 장난스러운 마무리를 더하면서 로리타 차림 전체를 하나로 묶어 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KimonoHeadwear.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KimonoHeadwear.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 기모노 머리장식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KimonoHeadwear.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KimonoHeadwear.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기모노 세트용 장식 머리장식입니다. 의상을 압도하지 않으면서 격식 있는 전통 포인트를 더하도록 만들어졌습니다. 착용자에게 더 의례적이고 정성스럽게 차려입은 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NurseCap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NurseCap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 간호사 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NurseCap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NurseCap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순한 의료 형태와 분명한 전문직 스타일을 갖춘 깨끗한 간호사 모자입니다. 간호사 제복과 어울리며, 고양이 귀 주변에서도 잘 보이도록 높게 착용합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KiiroRibbon.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KiiroRibbon.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 리본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KiiroRibbon.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KiiroRibbon.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차분하고 세련된 형태의 어두운 리본 머리 장식입니다. 머리 곁에 부드럽고 우아한 포인트를 더해 격조 있는 일상 차림에 잘 어울립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NunCap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NunCap.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 수녀 두건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_NunCap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_NunCap.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수녀복에 맞춰 만든 정숙한 수녀 두건입니다. 흑백 천이 머리를 단정하게 감싸며 조용하고 엄숙한 신앙의 차림을 완성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_BaoziHair.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_BaoziHair.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 만두머리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_BaoziHair.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_BaoziHair.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧은 치파오 한 벌에 맞춰 만든 한 쌍의 만두머리 장식입니다. 머리 윤곽을 단정하게 잡아 주며 귀여운 동양풍 실루엣으로 차림을 완성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenHat.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenHat.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 초등학교 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_KindergartenHat.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_KindergartenHat.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순하고 눈에 잘 띄는 형태의 아이용 초등학교 모자입니다. 소풍과 통학, 단체 활동에 어울리며, 차림 전체에 또렷한 학교 분위기를 더하는 동시에 착용자가 더 바른 학습 자세를 지키도록 도와줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_BakerKerchief.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_BakerKerchief.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 제빵사 두건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_BakerKerchief.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_BakerKerchief.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 제빵점 제복과 맞춰 쓰도록 만든 부드러운 제빵사 두건입니다. 제빵점 차림을 단정하고 따뜻하게 유지하면서도 일상적인 제빵과 계산대 업무에 부담 없을 만큼 가볍습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishHeadwear.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishHeadwear.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 물고기 머리장식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_FishHeadwear.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_FishHeadwear.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물고기 고양이 코스프레용으로 만든 밝은 머리장식으로, 경쾌한 수중 분위기를 냅니다. 키이로 물고기 고양이 한 벌의 마무리를 장식하며 어울리는 옷과 신발, 물고기 꼬리를 하나로 묶어 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkTail.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkTail.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 상어 꼬리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_SharkTail.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_SharkTail.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상어 코스프레용으로 만든 상어 꼬리 장식으로, 매끄럽고 생기 있는 실루엣을 지녔습니다. 수영복, 신발과 함께 키이로 상어 한 벌을 완성합니다. 설계자는 이것을 「심해 하키 상어에서 온 보습 슈트」라고 부르지만, 키이로에게 보습이 왜 필요할까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+KiiroFishTail.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KiiroFishTail.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 물고기 꼬리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+KiiroFishTail.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KiiroFishTail.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물고기 고양이 코스프레용으로 만든 물고기 꼬리 장식으로, 부드럽게 흔들리는 수중 형태를 지녔습니다. 어울리는 옷과 신발, 머리장식과 함께 키이로 물고기 고양이 한 벌을 완성합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Strappy_Panty.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Strappy_Panty.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 스트랩 란제리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+Kiiro_Strappy_Panty.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiiro_Strappy_Panty.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메이드복 아래에 입도록 설계된 섬세한 밝은색 스트랩 란제리 세트입니다. 가느다란 끈과 옅은 불투명 스타킹이 실루엣을 단정하고 우아하게 유지해, 격식 있는 서비스 복장의 세련된 안쪽 레이어로 적합합니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ThingDef+Kiiro_Swimsuit.label</x:t>
   </x:si>
   <x:si>
@@ -337,112 +1069,22 @@
     <x:t>단순하게 몸에 맞는 형태와 최소한의 장식만 갖춘 가벼운 수영복입니다. 더운 날씨에도 움직임을 유연하게 유지하며 물가에서의 여가에 깔끔한 여름 느낌을 줍니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>ThingDef+Kiiro_NurseUniform.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_NurseUniform.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 간호사 제복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_NurseUniform.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_NurseUniform.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단정한 의료 실루엣과 실용적인 재단을 갖춘 깨끗한 흰색과 파랑색 간호사 제복입니다. 병동과 진료소에서 믿음직해 보이며, 치료와 응급처치 중 빠르게 움직일 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Cookercap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cookercap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 셰프 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Cookercap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cookercap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드럽고 둥근 형태와 깔끔한 주방 스타일을 갖춘 가벼운 셰프 모자입니다. 셰프 제복을 완성하며 착용자를 깨끗하고 단정하며 주방 일을 할 준비가 된 모습으로 보이게 합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+ChildCat2Cap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChildCat2Cap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 어린이 망토 리본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+ChildCat2Cap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChildCat2Cap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어린이 망토 의상과 맞춰 쓰는 작고 어두운 리본 장식입니다. 머리 주변에 단정하고 장난스러운 마무리를 더하면서 전체 어린이 망토 세트를 조화롭게 유지합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_KimonoHeadwear.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_KimonoHeadwear.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 기모노 머리장식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_KimonoHeadwear.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_KimonoHeadwear.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기모노 세트용 장식 머리장식입니다. 의상을 압도하지 않으면서 격식 있는 전통 포인트를 더하도록 만들어졌습니다. 착용자에게 더 의례적이고 정성스럽게 차려입은 인상을 줍니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_NurseCap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_NurseCap.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 간호사 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_NurseCap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_NurseCap.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순한 의료 형태와 분명한 전문직 스타일을 갖춘 깨끗한 간호사 모자입니다. 간호사 제복과 어울리며, 고양이 귀 주변에서도 잘 보이도록 높게 착용합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_Strappy_Panty.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_Strappy_Panty.label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키이로 스트랩 란제리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThingDef+Kiiro_Strappy_Panty.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiiro_Strappy_Panty.description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메이드복 아래에 입도록 설계된 섬세한 밝은색 스트랩 란제리 세트입니다. 가느다란 끈과 옅은 불투명 스타킹이 실루엣을 단정하고 우아하게 유지해, 격식 있는 서비스 복장의 세련된 안쪽 레이어로 적합합니다.</x:t>
+    <x:t>ThingDef+CYQAQ_Apparel_Bangasa.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYQAQ_Apparel_Bangasa.label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 종이우산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ThingDef+CYQAQ_Apparel_Bangasa.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYQAQ_Apparel_Bangasa.description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키이로 고급 종이와 목재로 만든 키이로 전통 종이우산입니다. 우아한 우산면이 기모노를 비롯한 동양풍 차림에 잘 어울립니다. 비나 눈이 올 때 펼쳐지며, 차림에 조용하고 기품 있는 우천의 정취를 더합니다. (사실 비는 못 막습니다. 콜록콜록. 현실에서도 종이우산으로 비를 막는 사람은 거의 없잖아요?)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -807,7 +1449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F46"/>
+  <x:dimension ref="A1:F117"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="7" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -881,35 +1523,35 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>24</x:v>
@@ -923,7 +1565,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>27</x:v>
@@ -937,7 +1579,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>30</x:v>
@@ -951,517 +1593,1511 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
       <x:c r="A42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
       <x:c r="A43" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
       <x:c r="A44" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
       <x:c r="A45" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
       <x:c r="A46" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:6">
+      <x:c r="A47" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:6">
+      <x:c r="A48" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:6">
+      <x:c r="A49" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:6">
+      <x:c r="A50" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:6">
+      <x:c r="A51" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:6">
+      <x:c r="A52" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:6">
+      <x:c r="A53" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:6">
+      <x:c r="A54" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:6">
+      <x:c r="A55" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:6">
+      <x:c r="A56" s="1" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:6">
+      <x:c r="A57" s="1" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:6">
+      <x:c r="A58" s="1" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:6">
+      <x:c r="A59" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:6">
+      <x:c r="A60" s="1" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:6">
+      <x:c r="A61" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:6">
+      <x:c r="A62" s="1" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:6">
+      <x:c r="A63" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:6">
+      <x:c r="A64" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:6">
+      <x:c r="A65" s="1" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F65" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:6">
+      <x:c r="A66" s="1" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F66" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:6">
+      <x:c r="A67" s="1" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F67" s="1" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:6">
+      <x:c r="A68" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:6">
+      <x:c r="A69" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F69" s="1" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:6">
+      <x:c r="A70" s="1" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F70" s="1" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:6">
+      <x:c r="A71" s="1" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:6">
+      <x:c r="A72" s="1" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F72" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:6">
+      <x:c r="A73" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F73" s="1" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:6">
+      <x:c r="A74" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F74" s="1" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:6">
+      <x:c r="A75" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C75" s="1" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F75" s="1" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:6">
+      <x:c r="A76" s="1" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F76" s="1" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:6">
+      <x:c r="A77" s="1" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F77" s="1" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:6">
+      <x:c r="A78" s="1" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F78" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:6">
+      <x:c r="A79" s="1" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F79" s="1" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:6">
+      <x:c r="A80" s="1" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F80" s="1" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:6">
+      <x:c r="A81" s="1" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F81" s="1" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:6">
+      <x:c r="A82" s="1" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F82" s="1" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:6">
+      <x:c r="A83" s="1" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F83" s="1" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:6">
+      <x:c r="A84" s="1" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B84" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C84" s="1" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F84" s="1" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:6">
+      <x:c r="A85" s="1" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C85" s="1" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F85" s="1" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:6">
+      <x:c r="A86" s="1" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B86" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C86" s="1" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F86" s="1" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:6">
+      <x:c r="A87" s="1" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B87" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C87" s="1" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F87" s="1" t="s">
+        <x:v>266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:6">
+      <x:c r="A88" s="1" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B88" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C88" s="1" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F88" s="1" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:6">
+      <x:c r="A89" s="1" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B89" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C89" s="1" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F89" s="1" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:6">
+      <x:c r="A90" s="1" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B90" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C90" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F90" s="1" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:6">
+      <x:c r="A91" s="1" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B91" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F91" s="1" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:6">
+      <x:c r="A92" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F92" s="1" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:6">
+      <x:c r="A93" s="1" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B93" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F93" s="1" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:6">
+      <x:c r="A94" s="1" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B94" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C94" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F94" s="1" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:6">
+      <x:c r="A95" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F95" s="1" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:6">
+      <x:c r="A96" s="1" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B96" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F96" s="1" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:6">
+      <x:c r="A97" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F97" s="1" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:6">
+      <x:c r="A98" s="1" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B98" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F98" s="1" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:6">
+      <x:c r="A99" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B99" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F99" s="1" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:6">
+      <x:c r="A100" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F100" s="1" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:6">
+      <x:c r="A101" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F101" s="1" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:6">
+      <x:c r="A102" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B102" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F102" s="1" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:6">
+      <x:c r="A103" s="1" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F103" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:6">
+      <x:c r="A104" s="1" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F104" s="1" t="s">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:6">
+      <x:c r="A105" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B105" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C105" s="1" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F105" s="1" t="s">
+        <x:v>320</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:6">
+      <x:c r="A106" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B106" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C106" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F106" s="1" t="s">
+        <x:v>323</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:6">
+      <x:c r="A107" s="1" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B107" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C107" s="1" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F107" s="1" t="s">
+        <x:v>326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:6">
+      <x:c r="A108" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B108" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C108" s="1" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F108" s="1" t="s">
+        <x:v>329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:6">
+      <x:c r="A109" s="1" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B109" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C109" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F109" s="1" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:6">
+      <x:c r="A110" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B110" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C110" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F110" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:6">
+      <x:c r="A111" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B111" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C111" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F111" s="1" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:6">
+      <x:c r="A112" s="1" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B112" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C112" s="1" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="F112" s="1" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:6">
+      <x:c r="A113" s="1" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B113" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C113" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F113" s="1" t="s">
+        <x:v>344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:6">
+      <x:c r="A114" s="1" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B114" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C114" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F114" s="1" t="s">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:6">
+      <x:c r="A115" s="1" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B115" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C115" s="1" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="F115" s="1" t="s">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:6">
+      <x:c r="A116" s="1" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B116" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C116" s="1" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F116" s="1" t="s">
+        <x:v>353</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:6">
+      <x:c r="A117" s="1" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B117" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C117" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F117" s="1" t="s">
+        <x:v>356</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
